--- a/output.xlsx
+++ b/output.xlsx
@@ -24,7 +24,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -33,7 +33,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -42,7 +42,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -51,7 +51,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -60,7 +60,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -69,7 +69,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -79,7 +79,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="16"/>
+        <sz val="12"/>
         <color indexed="9"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -88,24 +88,16 @@
     </r>
     <r>
       <rPr>
-        <sz val="16"/>
+        <sz val="12"/>
         <color indexed="9"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t xml:space="preserve"> (D.d.t.) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color indexed="9"/>
-        <rFont val="Helvetica Neue"/>
-      </rPr>
-      <t xml:space="preserve">D.P.R. 472 del 14-08-1996 - D.P.R. 696 del 21-12-1996
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
+      <t xml:space="preserve"> (D.d.t.) D.P.R. 472 del 14-08-1996 - D.P.R. 696 del 21-12-1996
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -114,7 +106,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="7"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -123,7 +115,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="14"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -132,7 +124,7 @@
     <r>
       <rPr>
         <u val="single"/>
-        <sz val="14"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -140,7 +132,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="14"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -149,7 +141,7 @@
     <r>
       <rPr>
         <u val="single"/>
-        <sz val="14"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -159,7 +151,7 @@
     <r>
       <rPr>
         <u val="single"/>
-        <sz val="14"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -168,7 +160,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
@@ -632,7 +624,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -649,33 +641,18 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <sz val="13"/>
+      <sz val="12"/>
+      <color indexed="9"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="12"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color indexed="9"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color indexed="9"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="14"/>
+      <sz val="13"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
@@ -731,8 +708,18 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
       <sz val="16"/>
       <color indexed="11"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color indexed="9"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
@@ -846,7 +833,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -859,43 +846,46 @@
     <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="13" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="15" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="19" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="17" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="18" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="17" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="19" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="18" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="18" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1954,7 +1944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="7" width="16.3516" style="1" customWidth="1"/>
@@ -1992,7 +1982,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" ht="84" customHeight="1">
+    <row r="4" ht="83" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2054,7 +2044,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" ht="22.95" customHeight="1">
+    <row r="10" ht="23.95" customHeight="1">
       <c r="A10" t="s" s="7">
         <v>6</v>
       </c>
@@ -2249,97 +2239,106 @@
       <c r="F30" s="3"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" ht="25.9" customHeight="1">
+    <row r="31" ht="20.05" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" t="s" s="4">
+      <c r="F31" s="3"/>
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32" ht="25.9" customHeight="1">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" t="s" s="10">
         <v>9</v>
       </c>
-      <c r="G31" s="9"/>
-    </row>
-    <row r="32" ht="25.9" customHeight="1">
-      <c r="A32" t="s" s="10">
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" ht="25.9" customHeight="1">
+      <c r="A33" t="s" s="11">
         <v>10</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" t="s" s="10">
+      <c r="B33" s="3"/>
+      <c r="C33" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="D32" t="s" s="10">
+      <c r="D33" t="s" s="11">
         <v>12</v>
       </c>
-      <c r="E32" t="s" s="10">
+      <c r="E33" t="s" s="11">
         <v>13</v>
       </c>
-      <c r="F32" s="11"/>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" ht="27.35" customHeight="1">
-      <c r="A33" t="s" s="12">
+      <c r="F33" s="12"/>
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" ht="27.35" customHeight="1">
+      <c r="A34" t="s" s="13">
         <v>14</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" t="s" s="13">
-        <v>15</v>
-      </c>
-      <c r="E33" t="s" s="14">
-        <v>16</v>
-      </c>
-      <c r="F33" t="s" s="10">
-        <v>17</v>
-      </c>
-      <c r="G33" s="3"/>
-    </row>
-    <row r="34" ht="8.35" customHeight="1">
-      <c r="A34" t="s" s="10">
-        <v>18</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="D34" t="s" s="14">
+        <v>15</v>
+      </c>
       <c r="E34" t="s" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F34" t="s" s="11">
+        <v>17</v>
+      </c>
       <c r="G34" s="3"/>
     </row>
-    <row r="35" ht="8.15" customHeight="1">
-      <c r="A35" s="3"/>
+    <row r="35" ht="8.35" customHeight="1">
+      <c r="A35" t="s" s="11">
+        <v>18</v>
+      </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" t="s" s="10">
-        <v>20</v>
+      <c r="E35" t="s" s="16">
+        <v>19</v>
       </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3"/>
     </row>
-    <row r="36" ht="27.55" customHeight="1">
+    <row r="36" ht="8.15" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="F36" t="s" s="11">
+        <v>20</v>
+      </c>
       <c r="G36" s="3"/>
     </row>
     <row r="37" ht="27.55" customHeight="1">
-      <c r="A37" t="s" s="16">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" ht="27.55" customHeight="1">
+      <c r="A38" t="s" s="17">
         <v>21</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="36">
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:D8"/>
     <mergeCell ref="A9:C9"/>
@@ -2352,12 +2351,6 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B24:F24"/>
@@ -2367,14 +2360,21 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="F33:G34"/>
-    <mergeCell ref="F35:G36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="A34:D36"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="F34:G35"/>
+    <mergeCell ref="F36:G37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="A35:D37"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="79" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
